--- a/PLANTILLA_CONTROL_EVENTOS_CAMPUS_VILLA.xlsx
+++ b/PLANTILLA_CONTROL_EVENTOS_CAMPUS_VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7ED717-006E-4F3D-8FB2-ED866C496C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AB3291-DABE-4520-88C6-15763976DBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -247,18 +247,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventos" displayName="TablaEventos" ref="A1:I10" dataDxfId="0">
-  <autoFilter ref="A1:I10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventos" displayName="TablaEventos" ref="A1:I8" dataDxfId="9">
+  <autoFilter ref="A1:I8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evento / Actividad" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Requerimientos" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Prioridad" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Categoría" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Estado" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evento / Actividad" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Requerimientos" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Prioridad" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Categoría" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Estado" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -549,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="28" customWidth="1"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>45808</v>
+        <v>46173</v>
       </c>
       <c r="B5" s="4">
         <v>0.375</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>46904</v>
+        <v>46173</v>
       </c>
       <c r="B6" s="4">
         <v>0.375</v>
@@ -782,9 +782,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>46175</v>
-      </c>
+      <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -795,9 +793,7 @@
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>46176</v>
-      </c>
+      <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1005,28 +1001,6 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/PLANTILLA_CONTROL_EVENTOS_CAMPUS_VILLA.xlsx
+++ b/PLANTILLA_CONTROL_EVENTOS_CAMPUS_VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AB3291-DABE-4520-88C6-15763976DBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8FEB50-D190-4BF6-ADDA-28F85DC91862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
-  <si>
-    <t>Fecha</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="60">
   <si>
     <t>Hora</t>
   </si>
@@ -140,6 +137,103 @@
   </si>
   <si>
     <t>Corporativo</t>
+  </si>
+  <si>
+    <t>08;00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARRERA DE INGIENERIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concurso de Ingieneria Civil </t>
+  </si>
+  <si>
+    <t>mesas</t>
+  </si>
+  <si>
+    <t>Feria de Papers</t>
+  </si>
+  <si>
+    <t>24/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIENERIA AMBIENTAL </t>
+  </si>
+  <si>
+    <t>SOL 9606</t>
+  </si>
+  <si>
+    <t>Feria Ambiental 2026</t>
+  </si>
+  <si>
+    <t>Requerimiento:
+10 mesas con mantel
+20 sillas
+Tomas eléctricas cercanas o extensiones eléctricas para stands (de ser posible)
+Layout:
+Se requiere retirar los muebles del hall y colocar las mesas alrededor del espacio.
+La exhibición de EKOVA será reubicada hacia el lado de la escalera</t>
+  </si>
+  <si>
+    <t>Workshop de Líderes en Circularidad</t>
+  </si>
+  <si>
+    <t>sol 9697</t>
+  </si>
+  <si>
+    <t>Requerimiento:
+7 mesas con mantel
+49 sillas
+2 micrófonos inalámbricos con pilas nuevas
+Equipo de sonido operativo
+Proyector y conexión HDMI
+Mesa adicional para coffee break
+Layout:
+Se colocarán 07 mesas en formato workshop con 07 sillas por mesa.
+01 mesa será destinada al coffee break.
+Se requiere retirar los muebles del hall frente al auditorio, ya que se implementará un espacio para fotos y networking.
+Se requiere apoyo para el brandeo del espacio en coordinación con @Maria Luisa Leveau Besarez.</t>
+  </si>
+  <si>
+    <t>Alta - Sede Villa – Hall del Pabellón N</t>
+  </si>
+  <si>
+    <t>Alta - Hall del segundo piso – Pabellón O</t>
+  </si>
+  <si>
+    <t>sol 9608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciclo de Conferencias: “Zero Waste: Ecodiseño y Negocios Sostenibles” </t>
+  </si>
+  <si>
+    <t>Requerimiento:
+40 sillas
+Televisor con parante
+Podio
+Equipo de sonido con 2 micrófonos inalámbricos con pilas nuevas
+Extensión eléctrica
+Layout:
+Las sillas se colocarán en formato auditorio orientadas hacia el televisor.
+Se requiere retirar los muebles del hall.
+La exhibición de EKOVA será reubicada temporalmente.
+Se requiere apoyo para el brandeo del espacio en coordinación con @Maria Luisa Leveau Besarez.</t>
+  </si>
+  <si>
+    <t>sol 9609</t>
+  </si>
+  <si>
+    <t>Exhibición: Biomateriales – EKOVA </t>
+  </si>
+  <si>
+    <t>Instalación:
+22 de junio – 10:00 a.m.
+Retiro:
+06 de julio – 10:00 a.m.
+Sede Villa – Hall del Pabellón N
+Requerimiento:
+Retiro parcial de muebles para la implementación de la exhibición
+Apoyo para ingreso y salida de materiales</t>
   </si>
 </sst>
 </file>
@@ -186,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -197,6 +291,25 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -247,10 +360,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventos" displayName="TablaEventos" ref="A1:I8" dataDxfId="9">
-  <autoFilter ref="A1:I8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventos" displayName="TablaEventos" ref="A1:I15" dataDxfId="9">
+  <autoFilter ref="A1:I15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="24/06/2026" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="5"/>
@@ -549,71 +662,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46173</v>
       </c>
@@ -621,28 +734,28 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>46173</v>
       </c>
@@ -650,28 +763,28 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46173</v>
       </c>
@@ -679,28 +792,28 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>46173</v>
       </c>
@@ -708,26 +821,26 @@
         <v>0.375</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>46172</v>
       </c>
@@ -735,24 +848,24 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>46174</v>
       </c>
@@ -760,95 +873,203 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="360" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>46198</v>
+      </c>
+      <c r="B12" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="300" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>46198</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="180" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>46195</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -858,148 +1079,170 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
